--- a/manufacturing_forms/019_material_movement_audit_report_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/019_material_movement_audit_report_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'metal',_'label':_'metal'}</t>
+          <t>metal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Metal', 'label': 'Metal'}</t>
+          <t>Metal</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'plastic',_'label':_'plastic'}</t>
+          <t>plastic</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Plastic', 'label': 'Plastic'}</t>
+          <t>Plastic</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'glass',_'label':_'glass'}</t>
+          <t>glass</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Glass', 'label': 'Glass'}</t>
+          <t>Glass</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_123,_'label':_123}</t>
+          <t>123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 123, 'label': 123}</t>
+          <t>123</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_456,_'label':_456}</t>
+          <t>456</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 456, 'label': 456}</t>
+          <t>456</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_111,_'label':_111}</t>
+          <t>111</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 111, 'label': 111}</t>
+          <t>111</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_222,_'label':_222}</t>
+          <t>222</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 222, 'label': 222}</t>
+          <t>222</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'chatjimmy',_'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'chatjimmy', 'label': 'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'john',_'label':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'john', 'label': 'john'}</t>
+          <t>john</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_999,_'label':_999}</t>
+          <t>999</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 999, 'label': 999}</t>
+          <t>999</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_9999,_'label':_9999}</t>
+          <t>9999</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 9999, 'label': 9999}</t>
+          <t>9999</t>
         </is>
       </c>
     </row>
